--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67ABCD1-10F1-4A8C-A964-C0B939A53AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCEC3AA-5619-4D12-87C6-FDEDD5BE1196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30540" yWindow="3285" windowWidth="32745" windowHeight="15285" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-34890" yWindow="1425" windowWidth="32745" windowHeight="15285" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -44,12 +44,42 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>locatives</t>
+    <t>base_id</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>{我}{在}{</t>
+    <t>hook_title</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hook_image_path</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>situation_subtitle</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cta_text</t>
+  </si>
+  <si>
+    <t>syllable_times_ms</t>
+  </si>
+  <si>
+    <t>sound_path</t>
+  </si>
+  <si>
+    <t>과일 가게에서 급한 상황을 중국어로 말해보세요.</t>
+  </si>
+  <si>
+    <t>더 많은 장소 묻기 본편 시청!</t>
+  </si>
+  <si>
+    <t>video_path</t>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/洗手</t>
     </r>
     <r>
       <rPr>
@@ -59,220 +89,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>这儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>저는 여기 있어요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>은행은 저기에 있어요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>어디 가세요?</t>
-  </si>
-  <si>
-    <r>
-      <t>얼화(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>儿</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>化):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 북방 지역에서는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(r)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>을 붙여 말하</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>去}{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哪儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>}?</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>银</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>行}{在}{那</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/video/locatives/我在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这儿</t>
+      <t>间在哪里</t>
     </r>
     <r>
       <rPr>
@@ -289,17 +106,17 @@
   </si>
   <si>
     <r>
-      <t>resource/video/locatives/</t>
+      <t>resource/sound/sentense/</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
+        <rFont val="Microsoft YaHei"/>
         <family val="2"/>
-        <charset val="136"/>
+        <charset val="134"/>
       </rPr>
-      <t>你去哪儿</t>
+      <t>洗手间在哪里</t>
     </r>
     <r>
       <rPr>
@@ -310,68 +127,13 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>.mp4</t>
+      <t>.mp3</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>resource/video/locatives/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>银行在那儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>base_id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hook_title</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hook_image_path</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>situation_subtitle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cta_text</t>
-  </si>
-  <si>
-    <t>syllable_times_ms</t>
-  </si>
-  <si>
-    <t>sound_path</t>
-  </si>
-  <si>
-    <t>fruit_store</t>
-  </si>
-  <si>
-    <r>
-      <t>과일</t>
+      <t>상하이 여행 중\n</t>
     </r>
     <r>
       <rPr>
@@ -391,7 +153,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>가게에서</t>
+      <t>갑자기</t>
     </r>
     <r>
       <rPr>
@@ -411,7 +173,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>갑자기</t>
+      <t>배가</t>
     </r>
     <r>
       <rPr>
@@ -431,26 +193,6 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>배가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
       <t>아프다면</t>
     </r>
     <r>
@@ -463,19 +205,18 @@
       </rPr>
       <t>?!</t>
     </r>
-  </si>
-  <si>
-    <t>과일 가게에서 급한 상황을 중국어로 말해보세요.</t>
-  </si>
-  <si>
-    <t>더 많은 장소 묻기 본편 시청!</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>where</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,50 +319,21 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans KR"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF57A64A"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF57A64A"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
       <charset val="129"/>
     </font>
     <font>
@@ -646,34 +358,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Noto Sans KR"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans KR"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans KR"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -763,9 +447,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -773,18 +469,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1131,9 +815,9 @@
     <col min="4" max="4" width="38.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="46" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="83.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="87" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="36.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="62.625" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
@@ -1149,25 +833,28 @@
         <v>0</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>19</v>
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
       </c>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
@@ -1177,19 +864,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>23</v>
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
@@ -1270,94 +963,49 @@
       <c r="L16" s="12"/>
       <c r="M16" s="12"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="3:13">
       <c r="D17" s="5"/>
       <c r="F17" s="4"/>
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="3:13">
       <c r="D18" s="6"/>
       <c r="E18" s="2"/>
       <c r="G18" s="4"/>
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="3:13">
       <c r="F19" s="4"/>
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="3:13">
       <c r="D20" s="7"/>
       <c r="E20" s="8"/>
       <c r="G20" s="4"/>
       <c r="L20" s="12"/>
       <c r="M20" s="12"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="3:13">
       <c r="F21" s="4"/>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="3:13">
       <c r="D28" s="9"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:13" ht="18">
-      <c r="A29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B29">
-        <v>99</v>
-      </c>
-      <c r="C29" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="18">
-      <c r="A30" t="s">
-        <v>2</v>
-      </c>
-      <c r="B30">
-        <v>100</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
+    <row r="29" spans="3:13">
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="3:13">
+      <c r="C30" s="7"/>
       <c r="F30" s="18"/>
     </row>
-    <row r="31" spans="1:13">
-      <c r="A31" t="s">
-        <v>2</v>
-      </c>
-      <c r="B31">
-        <v>101</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" t="s">
-        <v>11</v>
-      </c>
+    <row r="31" spans="3:13">
+      <c r="C31" s="7"/>
       <c r="G31" s="4"/>
     </row>
   </sheetData>

--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DCEC3AA-5619-4D12-87C6-FDEDD5BE1196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD67575C-4436-4483-BB7D-4445C05AC691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34890" yWindow="1425" windowWidth="32745" windowHeight="15285" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="3870" yWindow="11100" windowWidth="32745" windowHeight="15285" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -210,6 +210,9 @@
   <si>
     <t>where</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ko_narration_id</t>
   </si>
 </sst>
 </file>
@@ -838,22 +841,25 @@
       <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="3"/>
@@ -872,16 +878,19 @@
       <c r="D2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>12</v>
       </c>
       <c r="L2" s="12"/>

--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD67575C-4436-4483-BB7D-4445C05AC691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093EC5DD-81DB-45E1-988E-7E045AFE02B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="11100" windowWidth="32745" windowHeight="15285" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="17865" yWindow="5205" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -213,6 +213,7 @@
   </si>
   <si>
     <t>ko_narration_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>

--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093EC5DD-81DB-45E1-988E-7E045AFE02B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE38717-FE2E-40CA-ACEA-F44681229648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17865" yWindow="5205" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="360" yWindow="3855" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -60,19 +60,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>cta_text</t>
-  </si>
-  <si>
     <t>syllable_times_ms</t>
   </si>
   <si>
     <t>sound_path</t>
-  </si>
-  <si>
-    <t>과일 가게에서 급한 상황을 중국어로 말해보세요.</t>
-  </si>
-  <si>
-    <t>더 많은 장소 묻기 본편 시청!</t>
   </si>
   <si>
     <t>video_path</t>
@@ -132,8 +123,16 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>상하이 여행 중\n</t>
+    <t>where</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ko_narration_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>중국 여행 중\n</t>
     </r>
     <r>
       <rPr>
@@ -169,31 +168,11 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FFB5CEA8"/>
-        <rFont val="돋움"/>
+        <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>배가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>아프다면</t>
+      <t>급똥이 마렵다면</t>
     </r>
     <r>
       <rPr>
@@ -208,11 +187,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>where</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ko_narration_id</t>
+    <t>공용 화장실이면 휴지가 없을 확률이 크다</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -408,7 +383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -446,9 +421,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -818,8 +790,7 @@
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="46" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.75" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="42" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="36.75" bestFit="1" customWidth="1"/>
@@ -843,7 +814,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>4</v>
@@ -859,9 +830,6 @@
       </c>
       <c r="J1" t="s">
         <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
       </c>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
@@ -871,28 +839,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>9</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>14</v>
+      <c r="D2" s="20" t="s">
+        <v>13</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
         <v>9</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" t="s">
-        <v>12</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
@@ -904,7 +869,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="D4" s="8"/>
-      <c r="G4" s="14"/>
+      <c r="G4" s="13"/>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="4"/>
@@ -915,15 +880,15 @@
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="C6" s="16"/>
-      <c r="D6" s="15"/>
-      <c r="G6" s="17"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="14"/>
+      <c r="G6" s="16"/>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="G7" s="17"/>
+      <c r="G7" s="16"/>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
       <c r="O7" s="4"/>
@@ -953,7 +918,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="D12" s="10"/>
-      <c r="G12" s="20"/>
+      <c r="G12" s="19"/>
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
     </row>
@@ -1008,11 +973,11 @@
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="3:13">
-      <c r="G29" s="19"/>
+      <c r="G29" s="18"/>
     </row>
     <row r="30" spans="3:13">
       <c r="C30" s="7"/>
-      <c r="F30" s="18"/>
+      <c r="F30" s="17"/>
     </row>
     <row r="31" spans="3:13">
       <c r="C31" s="7"/>

--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE38717-FE2E-40CA-ACEA-F44681229648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21CFE37-65BC-415A-B8AE-4406578F7D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="3855" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -188,6 +188,92 @@
   </si>
   <si>
     <t>공용 화장실이면 휴지가 없을 확률이 크다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fruit_store</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 과일은 근(500g) 단위로 주문하는 편</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/苹果多少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/苹果多少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>discount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/sound/sentense/能不能便宜一点.mp3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/video/能不能便宜一点.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국에서 과일이 먹고 싶은데\n돈이 부족하다면</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 과일은 한국보다 많이 싼 편이다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 여행 중\n먹음직스러운 과일을 봤을 때?!</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -868,13 +954,59 @@
       <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="D4" s="8"/>
-      <c r="G4" s="13"/>
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>18</v>
+      </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <v>98</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
       <c r="O5" s="4"/>

--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21CFE37-65BC-415A-B8AE-4406578F7D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D433F00F-BF1D-4E50-B601-1AB54143CFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="2805" yWindow="6720" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -276,12 +276,78 @@
     <t>중국 여행 중\n먹음직스러운 과일을 봤을 때?!</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>xicha</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">쇼핑몰에서 길 못 찾는 사람\n필수 생존 중국어 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">헤이티는 喜(기쁠희) 茶(차차)로 '행복한 차'라는 뜻 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/喜茶在几</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>喜茶在几楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,6 +503,13 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -874,7 +947,7 @@
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.5" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="46" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.75" bestFit="1" customWidth="1"/>
@@ -1011,10 +1084,31 @@
       <c r="M5" s="12"/>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" spans="1:15">
-      <c r="C6" s="15"/>
-      <c r="D6" s="14"/>
-      <c r="G6" s="16"/>
+    <row r="6" spans="1:15" ht="18.75">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="15">
+        <v>10</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
       <c r="O6" s="4"/>

--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D433F00F-BF1D-4E50-B601-1AB54143CFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5654F1-E4BA-4FF7-9B23-1CC50D3A4902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="6720" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="15525" yWindow="5790" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -342,12 +342,18 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>last_hold_text</t>
+  </si>
+  <si>
+    <t>last_hold_sec</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -510,6 +516,12 @@
       <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFE394DC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -542,7 +554,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -604,6 +616,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -954,7 +969,7 @@
     <col min="9" max="9" width="42" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="36.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="62.625" customWidth="1"/>
-    <col min="12" max="12" width="52" customWidth="1"/>
+    <col min="12" max="12" width="13.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.625" customWidth="1"/>
     <col min="14" max="14" width="41" bestFit="1" customWidth="1"/>
   </cols>
@@ -990,6 +1005,12 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>31</v>
+      </c>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
     </row>

--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5654F1-E4BA-4FF7-9B23-1CC50D3A4902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD0A60E-FB0E-417D-8ADF-394C5F8D4540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15525" yWindow="5790" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-36450" yWindow="1950" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -347,6 +347,159 @@
   </si>
   <si>
     <t>last_hold_sec</t>
+  </si>
+  <si>
+    <t>hair1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미용실에서 머리 감겨주는데\n물이 너무 뜨거울 때</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/水</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>温</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>有点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>烫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>水温有点烫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국은 머리 길이가 더 짧게 짜르는 경우가 있음\n길이를 확실히 강조하자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hair2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장원영은 대륙에서도 유명하다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국에서 장원영 스타일로\n머리를 자르고 싶다면</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/我想剪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>张元英那样的发型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我想剪张元英那样的发型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -964,10 +1117,11 @@
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="46" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="52.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="62.625" customWidth="1"/>
     <col min="12" max="12" width="13.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.625" customWidth="1"/>
@@ -1134,13 +1288,60 @@
       <c r="M6" s="12"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:15">
-      <c r="G7" s="16"/>
+    <row r="7" spans="1:15" ht="18.75">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" t="s">
+        <v>41</v>
+      </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>
       <c r="O8" s="4"/>

--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD0A60E-FB0E-417D-8ADF-394C5F8D4540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EBC160-9F47-4237-8C0C-039E94F6686B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36450" yWindow="1950" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="12330" yWindow="3000" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -52,15 +52,8 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>hook_image_path</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>situation_subtitle</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>syllable_times_ms</t>
   </si>
   <si>
     <t>sound_path</t>
@@ -343,162 +336,160 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>last_hold_text</t>
+    <t>hair1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미용실에서 머리 감겨주는데\n물이 너무 뜨거울 때</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/水</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>温</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>有点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>烫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>水温有点烫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국은 머리 길이가 더 짧게 짜르는 경우가 있음\n길이를 확실히 강조하자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hair2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장원영은 대륙에서도 유명하다</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국에서 장원영 스타일로\n머리를 자르고 싶다면</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/我想剪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>张元英那样的发型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我想剪张元英那样的发型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>last_hold_sec</t>
-  </si>
-  <si>
-    <t>hair1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>미용실에서 머리 감겨주는데\n물이 너무 뜨거울 때</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/video/水</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>温</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>有点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>烫</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/sound/sentense/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水温有点烫</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp3</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>중국은 머리 길이가 더 짧게 짜르는 경우가 있음\n길이를 확실히 강조하자</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>hair2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>장원영은 대륙에서도 유명하다</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>중국에서 장원영 스타일로\n머리를 자르고 싶다면</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/video/我想剪</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>张元英那样的发型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/sound/sentense/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我想剪张元英那样的发型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp3</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1116,14 +1107,13 @@
     <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="70.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="70.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
+    <col min="8" max="8" width="52.375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="44.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="52.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="62.625" customWidth="1"/>
-    <col min="12" max="12" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.625" customWidth="1"/>
     <col min="14" max="14" width="41" bestFit="1" customWidth="1"/>
   </cols>
@@ -1142,28 +1132,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="21" t="s">
-        <v>31</v>
+      <c r="I1" s="21" t="s">
+        <v>38</v>
       </c>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
@@ -1173,25 +1154,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>9</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
       <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
@@ -1206,25 +1187,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="F4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
         <v>16</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" t="s">
-        <v>18</v>
       </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
@@ -1235,25 +1216,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
-      <c r="G5" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="F5" s="13" t="s">
         <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" t="s">
+        <v>19</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
@@ -1264,25 +1245,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6" s="15">
         <v>10</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="F6" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
         <v>27</v>
       </c>
-      <c r="I6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" t="s">
-        <v>28</v>
+      <c r="H6" t="s">
+        <v>26</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
@@ -1293,25 +1274,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>5</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" t="s">
-        <v>34</v>
+      <c r="F7" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
@@ -1322,25 +1303,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E8">
         <v>6</v>
       </c>
-      <c r="G8" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" t="s">
-        <v>41</v>
+      <c r="F8" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" t="s">
+        <v>36</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>

--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EBC160-9F47-4237-8C0C-039E94F6686B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EACA2C9-A87A-445C-AE51-A8A29EAE1E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12330" yWindow="3000" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -53,66 +53,6 @@
   </si>
   <si>
     <t>situation_subtitle</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>sound_path</t>
-  </si>
-  <si>
-    <t>video_path</t>
-  </si>
-  <si>
-    <r>
-      <t>resource/video/洗手</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>间在哪里</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/sound/sentense/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>洗手间在哪里</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp3</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -192,72 +132,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>resource/sound/sentense/苹果多少</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>钱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp3</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/video/苹果多少</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>钱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>discount</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>resource/sound/sentense/能不能便宜一点.mp3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>resource/video/能不能便宜一点.mp4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>중국에서 과일이 먹고 싶은데\n돈이 부족하다면</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -282,60 +160,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>resource/video/喜茶在几</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>楼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/sound/sentense/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>喜茶在几楼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp3</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>hair1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -344,81 +168,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>resource/video/水</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>温</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>有点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>烫</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/sound/sentense/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水温有点烫</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp3</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>중국은 머리 길이가 더 짧게 짜르는 경우가 있음\n길이를 확실히 강조하자</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -435,61 +184,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>resource/video/我想剪</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>张元英那样的发型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/sound/sentense/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我想剪张元英那样的发型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp3</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>last_hold_sec</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bg_path</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/sound/bg_user/Moonlight_Over_The_Stone_Path.mp3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -497,7 +200,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -520,13 +223,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -653,13 +349,6 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="9"/>
@@ -702,40 +391,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -760,9 +452,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1105,12 +794,12 @@
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="70.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46" customWidth="1"/>
-    <col min="8" max="8" width="52.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="59.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="44.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="52.375" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="13.125" bestFit="1" customWidth="1"/>
@@ -1132,19 +821,16 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="21" t="s">
-        <v>38</v>
+      <c r="G1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>24</v>
       </c>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
@@ -1154,25 +840,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>9</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
         <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>7</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
@@ -1187,25 +867,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
@@ -1216,83 +890,68 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
       <c r="O5" s="4"/>
     </row>
-    <row r="6" spans="1:15" ht="18.75">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" s="15">
         <v>10</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>4</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12"/>
       <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:15" ht="18.75">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>5</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
@@ -1303,25 +962,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C8">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E8">
         <v>6</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12"/>

--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EACA2C9-A87A-445C-AE51-A8A29EAE1E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD234197-E007-436C-AE54-1ECF8C434F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-34830" yWindow="5925" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -195,12 +195,39 @@
     <t>resource/sound/bg_user/Moonlight_Over_The_Stone_Path.mp3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>구독 좋아요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ko_narration_line_id</t>
+  </si>
+  <si>
+    <t>고수\n테스트중</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>xiangcai</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1|2|3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1|2|4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sub_sentence_id</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,20 +290,6 @@
       <color rgb="FF4EC9B0"/>
       <name val="Consolas"/>
       <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF57A64A"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF57A64A"/>
-      <name val="Consolas"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -353,6 +366,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FFE394DC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -387,7 +406,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -404,12 +423,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -424,7 +437,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -449,9 +468,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -795,12 +811,11 @@
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="70.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="59.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="70.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="52.375" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="13.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="41.625" customWidth="1"/>
@@ -808,31 +823,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="I1" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="3"/>
       <c r="O1" s="3"/>
     </row>
     <row r="2" spans="1:15">
@@ -845,22 +865,16 @@
       <c r="C2">
         <v>9</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
       <c r="O2" s="4"/>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4">
@@ -872,17 +886,15 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4" s="13" t="s">
+      <c r="H4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15">
@@ -895,17 +907,15 @@
       <c r="C5">
         <v>98</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5" s="13" t="s">
+      <c r="H5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15">
@@ -915,20 +925,18 @@
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="13">
         <v>10</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6" s="16" t="s">
+      <c r="H6" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15">
@@ -941,20 +949,18 @@
       <c r="C7">
         <v>13</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
         <v>19</v>
       </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7" s="16" t="s">
+      <c r="H7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="G7" t="s">
+      <c r="J7" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15">
@@ -967,102 +973,121 @@
       <c r="C8">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="G8" t="s">
         <v>23</v>
       </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8" s="13" t="s">
+      <c r="H8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
       <c r="O8" s="4"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="G9" s="7"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="5">
+        <v>10</v>
+      </c>
       <c r="O9" s="4"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
       <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:15">
       <c r="D11" s="1"/>
       <c r="F11" s="4"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="D12" s="10"/>
-      <c r="G12" s="19"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
+      <c r="D12" s="8"/>
+      <c r="G12" s="17"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
     </row>
     <row r="17" spans="3:13">
-      <c r="D17" s="5"/>
       <c r="F17" s="4"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
     </row>
     <row r="18" spans="3:13">
-      <c r="D18" s="6"/>
       <c r="E18" s="2"/>
       <c r="G18" s="4"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
     </row>
     <row r="19" spans="3:13">
       <c r="F19" s="4"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
     </row>
     <row r="20" spans="3:13">
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
+      <c r="E20" s="6"/>
       <c r="G20" s="4"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
     </row>
     <row r="21" spans="3:13">
       <c r="F21" s="4"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
     </row>
     <row r="28" spans="3:13">
-      <c r="D28" s="9"/>
+      <c r="D28" s="7"/>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="3:13">
-      <c r="G29" s="18"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="3:13">
-      <c r="C30" s="7"/>
-      <c r="F30" s="17"/>
+      <c r="C30" s="5"/>
+      <c r="F30" s="15"/>
     </row>
     <row r="31" spans="3:13">
-      <c r="C31" s="7"/>
+      <c r="C31" s="5"/>
       <c r="G31" s="4"/>
     </row>
   </sheetData>

--- a/resource/table/shorts_conversation_clips.xlsx
+++ b/resource/table/shorts_conversation_clips.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,6 +753,112 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>payment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>중국 식당에서 당황 안하는
+필수 결제 표현</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>더 많은 문장이 궁금하다면 댓글 참고!</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1|2|3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1|2|3</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>resource/sound/bg_short/쇼츠-밝음.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>coldwater</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>중국 식당에서 더워 죽겠는데
+뜨거운 물이 나와 당황했다면</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>더 많은 문장이 궁금하다면 댓글 참고!</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1|2|3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1|2|11</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>resource/sound/bg_short/쇼츠-통통.mp3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
